--- a/docs/04_営業ツール/管理シート/営業管理（テレアポ・戦略・料金）.xlsx
+++ b/docs/04_営業ツール/管理シート/営業管理（テレアポ・戦略・料金）.xlsx
@@ -22,6 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="担当別Todo" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方ガイド" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="消費者フォローメール" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成約追跡" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="有料化管理" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'テレアポ管理（鹿児島）'!$A$1:$V$101</definedName>
@@ -35,8 +37,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="13">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +112,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +164,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+        <bgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
+        <bgColor rgb="00F8F9FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -333,6 +355,27 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4081,6 +4124,1570 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>リードID</t>
+        </is>
+      </c>
+      <c r="B1" s="44" t="inlineStr">
+        <is>
+          <t>リード日</t>
+        </is>
+      </c>
+      <c r="C1" s="44" t="inlineStr">
+        <is>
+          <t>消費者名</t>
+        </is>
+      </c>
+      <c r="D1" s="44" t="inlineStr">
+        <is>
+          <t>紹介工務店</t>
+        </is>
+      </c>
+      <c r="E1" s="44" t="inlineStr">
+        <is>
+          <t>リード種別</t>
+        </is>
+      </c>
+      <c r="F1" s="44" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="G1" s="44" t="inlineStr">
+        <is>
+          <t>商談開始日</t>
+        </is>
+      </c>
+      <c r="H1" s="44" t="inlineStr">
+        <is>
+          <t>契約日</t>
+        </is>
+      </c>
+      <c r="I1" s="44" t="inlineStr">
+        <is>
+          <t>契約金額</t>
+        </is>
+      </c>
+      <c r="J1" s="44" t="inlineStr">
+        <is>
+          <t>報酬率</t>
+        </is>
+      </c>
+      <c r="K1" s="44" t="inlineStr">
+        <is>
+          <t>成約報酬額</t>
+        </is>
+      </c>
+      <c r="L1" s="44" t="inlineStr">
+        <is>
+          <t>請求日</t>
+        </is>
+      </c>
+      <c r="M1" s="44" t="inlineStr">
+        <is>
+          <t>入金日</t>
+        </is>
+      </c>
+      <c r="N1" s="44" t="inlineStr">
+        <is>
+          <t>入金額</t>
+        </is>
+      </c>
+      <c r="O1" s="44" t="inlineStr">
+        <is>
+          <t>フォロー1回目</t>
+        </is>
+      </c>
+      <c r="P1" s="44" t="inlineStr">
+        <is>
+          <t>フォロー2回目</t>
+        </is>
+      </c>
+      <c r="Q1" s="44" t="inlineStr">
+        <is>
+          <t>フォロー3回目</t>
+        </is>
+      </c>
+      <c r="R1" s="44" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="45" t="n"/>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="45" t="n"/>
+      <c r="K2" s="46">
+        <f>I2*J2</f>
+        <v/>
+      </c>
+      <c r="L2" s="45" t="n"/>
+      <c r="M2" s="45" t="n"/>
+      <c r="N2" s="45" t="n"/>
+      <c r="O2" s="45" t="n"/>
+      <c r="P2" s="45" t="n"/>
+      <c r="Q2" s="45" t="n"/>
+      <c r="R2" s="45" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="47" t="n"/>
+      <c r="B3" s="47" t="n"/>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="47" t="n"/>
+      <c r="E3" s="47" t="n"/>
+      <c r="F3" s="47" t="n"/>
+      <c r="G3" s="47" t="n"/>
+      <c r="H3" s="47" t="n"/>
+      <c r="I3" s="47" t="n"/>
+      <c r="J3" s="47" t="n"/>
+      <c r="K3" s="48">
+        <f>I3*J3</f>
+        <v/>
+      </c>
+      <c r="L3" s="47" t="n"/>
+      <c r="M3" s="47" t="n"/>
+      <c r="N3" s="47" t="n"/>
+      <c r="O3" s="47" t="n"/>
+      <c r="P3" s="47" t="n"/>
+      <c r="Q3" s="47" t="n"/>
+      <c r="R3" s="47" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="n"/>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="46">
+        <f>I4*J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="45" t="n"/>
+      <c r="M4" s="45" t="n"/>
+      <c r="N4" s="45" t="n"/>
+      <c r="O4" s="45" t="n"/>
+      <c r="P4" s="45" t="n"/>
+      <c r="Q4" s="45" t="n"/>
+      <c r="R4" s="45" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="n"/>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="48">
+        <f>I5*J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="47" t="n"/>
+      <c r="O5" s="47" t="n"/>
+      <c r="P5" s="47" t="n"/>
+      <c r="Q5" s="47" t="n"/>
+      <c r="R5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="n"/>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
+      <c r="F6" s="45" t="n"/>
+      <c r="G6" s="45" t="n"/>
+      <c r="H6" s="45" t="n"/>
+      <c r="I6" s="45" t="n"/>
+      <c r="J6" s="45" t="n"/>
+      <c r="K6" s="46">
+        <f>I6*J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="45" t="n"/>
+      <c r="M6" s="45" t="n"/>
+      <c r="N6" s="45" t="n"/>
+      <c r="O6" s="45" t="n"/>
+      <c r="P6" s="45" t="n"/>
+      <c r="Q6" s="45" t="n"/>
+      <c r="R6" s="45" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="n"/>
+      <c r="B7" s="47" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="47" t="n"/>
+      <c r="E7" s="47" t="n"/>
+      <c r="F7" s="47" t="n"/>
+      <c r="G7" s="47" t="n"/>
+      <c r="H7" s="47" t="n"/>
+      <c r="I7" s="47" t="n"/>
+      <c r="J7" s="47" t="n"/>
+      <c r="K7" s="48">
+        <f>I7*J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="47" t="n"/>
+      <c r="M7" s="47" t="n"/>
+      <c r="N7" s="47" t="n"/>
+      <c r="O7" s="47" t="n"/>
+      <c r="P7" s="47" t="n"/>
+      <c r="Q7" s="47" t="n"/>
+      <c r="R7" s="47" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="n"/>
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="45" t="n"/>
+      <c r="G8" s="45" t="n"/>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="45" t="n"/>
+      <c r="J8" s="45" t="n"/>
+      <c r="K8" s="46">
+        <f>I8*J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="45" t="n"/>
+      <c r="M8" s="45" t="n"/>
+      <c r="N8" s="45" t="n"/>
+      <c r="O8" s="45" t="n"/>
+      <c r="P8" s="45" t="n"/>
+      <c r="Q8" s="45" t="n"/>
+      <c r="R8" s="45" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="n"/>
+      <c r="B9" s="47" t="n"/>
+      <c r="C9" s="47" t="n"/>
+      <c r="D9" s="47" t="n"/>
+      <c r="E9" s="47" t="n"/>
+      <c r="F9" s="47" t="n"/>
+      <c r="G9" s="47" t="n"/>
+      <c r="H9" s="47" t="n"/>
+      <c r="I9" s="47" t="n"/>
+      <c r="J9" s="47" t="n"/>
+      <c r="K9" s="48">
+        <f>I9*J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="47" t="n"/>
+      <c r="M9" s="47" t="n"/>
+      <c r="N9" s="47" t="n"/>
+      <c r="O9" s="47" t="n"/>
+      <c r="P9" s="47" t="n"/>
+      <c r="Q9" s="47" t="n"/>
+      <c r="R9" s="47" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="n"/>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="45" t="n"/>
+      <c r="H10" s="45" t="n"/>
+      <c r="I10" s="45" t="n"/>
+      <c r="J10" s="45" t="n"/>
+      <c r="K10" s="46">
+        <f>I10*J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="45" t="n"/>
+      <c r="M10" s="45" t="n"/>
+      <c r="N10" s="45" t="n"/>
+      <c r="O10" s="45" t="n"/>
+      <c r="P10" s="45" t="n"/>
+      <c r="Q10" s="45" t="n"/>
+      <c r="R10" s="45" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="n"/>
+      <c r="B11" s="47" t="n"/>
+      <c r="C11" s="47" t="n"/>
+      <c r="D11" s="47" t="n"/>
+      <c r="E11" s="47" t="n"/>
+      <c r="F11" s="47" t="n"/>
+      <c r="G11" s="47" t="n"/>
+      <c r="H11" s="47" t="n"/>
+      <c r="I11" s="47" t="n"/>
+      <c r="J11" s="47" t="n"/>
+      <c r="K11" s="48">
+        <f>I11*J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="47" t="n"/>
+      <c r="M11" s="47" t="n"/>
+      <c r="N11" s="47" t="n"/>
+      <c r="O11" s="47" t="n"/>
+      <c r="P11" s="47" t="n"/>
+      <c r="Q11" s="47" t="n"/>
+      <c r="R11" s="47" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="n"/>
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="45" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="45" t="n"/>
+      <c r="K12" s="46">
+        <f>I12*J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="45" t="n"/>
+      <c r="M12" s="45" t="n"/>
+      <c r="N12" s="45" t="n"/>
+      <c r="O12" s="45" t="n"/>
+      <c r="P12" s="45" t="n"/>
+      <c r="Q12" s="45" t="n"/>
+      <c r="R12" s="45" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="n"/>
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="47" t="n"/>
+      <c r="D13" s="47" t="n"/>
+      <c r="E13" s="47" t="n"/>
+      <c r="F13" s="47" t="n"/>
+      <c r="G13" s="47" t="n"/>
+      <c r="H13" s="47" t="n"/>
+      <c r="I13" s="47" t="n"/>
+      <c r="J13" s="47" t="n"/>
+      <c r="K13" s="48">
+        <f>I13*J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="47" t="n"/>
+      <c r="M13" s="47" t="n"/>
+      <c r="N13" s="47" t="n"/>
+      <c r="O13" s="47" t="n"/>
+      <c r="P13" s="47" t="n"/>
+      <c r="Q13" s="47" t="n"/>
+      <c r="R13" s="47" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="n"/>
+      <c r="B14" s="45" t="n"/>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="45" t="n"/>
+      <c r="G14" s="45" t="n"/>
+      <c r="H14" s="45" t="n"/>
+      <c r="I14" s="45" t="n"/>
+      <c r="J14" s="45" t="n"/>
+      <c r="K14" s="46">
+        <f>I14*J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="45" t="n"/>
+      <c r="M14" s="45" t="n"/>
+      <c r="N14" s="45" t="n"/>
+      <c r="O14" s="45" t="n"/>
+      <c r="P14" s="45" t="n"/>
+      <c r="Q14" s="45" t="n"/>
+      <c r="R14" s="45" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="n"/>
+      <c r="B15" s="47" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="47" t="n"/>
+      <c r="E15" s="47" t="n"/>
+      <c r="F15" s="47" t="n"/>
+      <c r="G15" s="47" t="n"/>
+      <c r="H15" s="47" t="n"/>
+      <c r="I15" s="47" t="n"/>
+      <c r="J15" s="47" t="n"/>
+      <c r="K15" s="48">
+        <f>I15*J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="47" t="n"/>
+      <c r="M15" s="47" t="n"/>
+      <c r="N15" s="47" t="n"/>
+      <c r="O15" s="47" t="n"/>
+      <c r="P15" s="47" t="n"/>
+      <c r="Q15" s="47" t="n"/>
+      <c r="R15" s="47" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="45" t="n"/>
+      <c r="G16" s="45" t="n"/>
+      <c r="H16" s="45" t="n"/>
+      <c r="I16" s="45" t="n"/>
+      <c r="J16" s="45" t="n"/>
+      <c r="K16" s="46">
+        <f>I16*J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="45" t="n"/>
+      <c r="M16" s="45" t="n"/>
+      <c r="N16" s="45" t="n"/>
+      <c r="O16" s="45" t="n"/>
+      <c r="P16" s="45" t="n"/>
+      <c r="Q16" s="45" t="n"/>
+      <c r="R16" s="45" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="n"/>
+      <c r="B17" s="47" t="n"/>
+      <c r="C17" s="47" t="n"/>
+      <c r="D17" s="47" t="n"/>
+      <c r="E17" s="47" t="n"/>
+      <c r="F17" s="47" t="n"/>
+      <c r="G17" s="47" t="n"/>
+      <c r="H17" s="47" t="n"/>
+      <c r="I17" s="47" t="n"/>
+      <c r="J17" s="47" t="n"/>
+      <c r="K17" s="48">
+        <f>I17*J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="47" t="n"/>
+      <c r="M17" s="47" t="n"/>
+      <c r="N17" s="47" t="n"/>
+      <c r="O17" s="47" t="n"/>
+      <c r="P17" s="47" t="n"/>
+      <c r="Q17" s="47" t="n"/>
+      <c r="R17" s="47" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n"/>
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+      <c r="H18" s="45" t="n"/>
+      <c r="I18" s="45" t="n"/>
+      <c r="J18" s="45" t="n"/>
+      <c r="K18" s="46">
+        <f>I18*J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="45" t="n"/>
+      <c r="M18" s="45" t="n"/>
+      <c r="N18" s="45" t="n"/>
+      <c r="O18" s="45" t="n"/>
+      <c r="P18" s="45" t="n"/>
+      <c r="Q18" s="45" t="n"/>
+      <c r="R18" s="45" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="n"/>
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="47" t="n"/>
+      <c r="E19" s="47" t="n"/>
+      <c r="F19" s="47" t="n"/>
+      <c r="G19" s="47" t="n"/>
+      <c r="H19" s="47" t="n"/>
+      <c r="I19" s="47" t="n"/>
+      <c r="J19" s="47" t="n"/>
+      <c r="K19" s="48">
+        <f>I19*J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="47" t="n"/>
+      <c r="M19" s="47" t="n"/>
+      <c r="N19" s="47" t="n"/>
+      <c r="O19" s="47" t="n"/>
+      <c r="P19" s="47" t="n"/>
+      <c r="Q19" s="47" t="n"/>
+      <c r="R19" s="47" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n"/>
+      <c r="B20" s="45" t="n"/>
+      <c r="C20" s="45" t="n"/>
+      <c r="D20" s="45" t="n"/>
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="45" t="n"/>
+      <c r="G20" s="45" t="n"/>
+      <c r="H20" s="45" t="n"/>
+      <c r="I20" s="45" t="n"/>
+      <c r="J20" s="45" t="n"/>
+      <c r="K20" s="46">
+        <f>I20*J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="45" t="n"/>
+      <c r="N20" s="45" t="n"/>
+      <c r="O20" s="45" t="n"/>
+      <c r="P20" s="45" t="n"/>
+      <c r="Q20" s="45" t="n"/>
+      <c r="R20" s="45" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n"/>
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="47" t="n"/>
+      <c r="E21" s="47" t="n"/>
+      <c r="F21" s="47" t="n"/>
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
+      <c r="I21" s="47" t="n"/>
+      <c r="J21" s="47" t="n"/>
+      <c r="K21" s="48">
+        <f>I21*J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="47" t="n"/>
+      <c r="M21" s="47" t="n"/>
+      <c r="N21" s="47" t="n"/>
+      <c r="O21" s="47" t="n"/>
+      <c r="P21" s="47" t="n"/>
+      <c r="Q21" s="47" t="n"/>
+      <c r="R21" s="47" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n"/>
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="45" t="n"/>
+      <c r="G22" s="45" t="n"/>
+      <c r="H22" s="45" t="n"/>
+      <c r="I22" s="45" t="n"/>
+      <c r="J22" s="45" t="n"/>
+      <c r="K22" s="46">
+        <f>I22*J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="45" t="n"/>
+      <c r="M22" s="45" t="n"/>
+      <c r="N22" s="45" t="n"/>
+      <c r="O22" s="45" t="n"/>
+      <c r="P22" s="45" t="n"/>
+      <c r="Q22" s="45" t="n"/>
+      <c r="R22" s="45" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="47" t="n"/>
+      <c r="B23" s="47" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="47" t="n"/>
+      <c r="E23" s="47" t="n"/>
+      <c r="F23" s="47" t="n"/>
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
+      <c r="I23" s="47" t="n"/>
+      <c r="J23" s="47" t="n"/>
+      <c r="K23" s="48">
+        <f>I23*J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="47" t="n"/>
+      <c r="M23" s="47" t="n"/>
+      <c r="N23" s="47" t="n"/>
+      <c r="O23" s="47" t="n"/>
+      <c r="P23" s="47" t="n"/>
+      <c r="Q23" s="47" t="n"/>
+      <c r="R23" s="47" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n"/>
+      <c r="B24" s="45" t="n"/>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="45" t="n"/>
+      <c r="G24" s="45" t="n"/>
+      <c r="H24" s="45" t="n"/>
+      <c r="I24" s="45" t="n"/>
+      <c r="J24" s="45" t="n"/>
+      <c r="K24" s="46">
+        <f>I24*J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+      <c r="N24" s="45" t="n"/>
+      <c r="O24" s="45" t="n"/>
+      <c r="P24" s="45" t="n"/>
+      <c r="Q24" s="45" t="n"/>
+      <c r="R24" s="45" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="n"/>
+      <c r="B25" s="47" t="n"/>
+      <c r="C25" s="47" t="n"/>
+      <c r="D25" s="47" t="n"/>
+      <c r="E25" s="47" t="n"/>
+      <c r="F25" s="47" t="n"/>
+      <c r="G25" s="47" t="n"/>
+      <c r="H25" s="47" t="n"/>
+      <c r="I25" s="47" t="n"/>
+      <c r="J25" s="47" t="n"/>
+      <c r="K25" s="48">
+        <f>I25*J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="47" t="n"/>
+      <c r="M25" s="47" t="n"/>
+      <c r="N25" s="47" t="n"/>
+      <c r="O25" s="47" t="n"/>
+      <c r="P25" s="47" t="n"/>
+      <c r="Q25" s="47" t="n"/>
+      <c r="R25" s="47" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n"/>
+      <c r="B26" s="45" t="n"/>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="45" t="n"/>
+      <c r="G26" s="45" t="n"/>
+      <c r="H26" s="45" t="n"/>
+      <c r="I26" s="45" t="n"/>
+      <c r="J26" s="45" t="n"/>
+      <c r="K26" s="46">
+        <f>I26*J26</f>
+        <v/>
+      </c>
+      <c r="L26" s="45" t="n"/>
+      <c r="M26" s="45" t="n"/>
+      <c r="N26" s="45" t="n"/>
+      <c r="O26" s="45" t="n"/>
+      <c r="P26" s="45" t="n"/>
+      <c r="Q26" s="45" t="n"/>
+      <c r="R26" s="45" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="n"/>
+      <c r="B27" s="47" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="47" t="n"/>
+      <c r="E27" s="47" t="n"/>
+      <c r="F27" s="47" t="n"/>
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="47" t="n"/>
+      <c r="I27" s="47" t="n"/>
+      <c r="J27" s="47" t="n"/>
+      <c r="K27" s="48">
+        <f>I27*J27</f>
+        <v/>
+      </c>
+      <c r="L27" s="47" t="n"/>
+      <c r="M27" s="47" t="n"/>
+      <c r="N27" s="47" t="n"/>
+      <c r="O27" s="47" t="n"/>
+      <c r="P27" s="47" t="n"/>
+      <c r="Q27" s="47" t="n"/>
+      <c r="R27" s="47" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n"/>
+      <c r="B28" s="45" t="n"/>
+      <c r="C28" s="45" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="45" t="n"/>
+      <c r="G28" s="45" t="n"/>
+      <c r="H28" s="45" t="n"/>
+      <c r="I28" s="45" t="n"/>
+      <c r="J28" s="45" t="n"/>
+      <c r="K28" s="46">
+        <f>I28*J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="45" t="n"/>
+      <c r="M28" s="45" t="n"/>
+      <c r="N28" s="45" t="n"/>
+      <c r="O28" s="45" t="n"/>
+      <c r="P28" s="45" t="n"/>
+      <c r="Q28" s="45" t="n"/>
+      <c r="R28" s="45" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="47" t="n"/>
+      <c r="B29" s="47" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="47" t="n"/>
+      <c r="E29" s="47" t="n"/>
+      <c r="F29" s="47" t="n"/>
+      <c r="G29" s="47" t="n"/>
+      <c r="H29" s="47" t="n"/>
+      <c r="I29" s="47" t="n"/>
+      <c r="J29" s="47" t="n"/>
+      <c r="K29" s="48">
+        <f>I29*J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="47" t="n"/>
+      <c r="M29" s="47" t="n"/>
+      <c r="N29" s="47" t="n"/>
+      <c r="O29" s="47" t="n"/>
+      <c r="P29" s="47" t="n"/>
+      <c r="Q29" s="47" t="n"/>
+      <c r="R29" s="47" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n"/>
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="45" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="45" t="n"/>
+      <c r="H30" s="45" t="n"/>
+      <c r="I30" s="45" t="n"/>
+      <c r="J30" s="45" t="n"/>
+      <c r="K30" s="46">
+        <f>I30*J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="45" t="n"/>
+      <c r="N30" s="45" t="n"/>
+      <c r="O30" s="45" t="n"/>
+      <c r="P30" s="45" t="n"/>
+      <c r="Q30" s="45" t="n"/>
+      <c r="R30" s="45" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="47" t="n"/>
+      <c r="B31" s="47" t="n"/>
+      <c r="C31" s="47" t="n"/>
+      <c r="D31" s="47" t="n"/>
+      <c r="E31" s="47" t="n"/>
+      <c r="F31" s="47" t="n"/>
+      <c r="G31" s="47" t="n"/>
+      <c r="H31" s="47" t="n"/>
+      <c r="I31" s="47" t="n"/>
+      <c r="J31" s="47" t="n"/>
+      <c r="K31" s="48">
+        <f>I31*J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="47" t="n"/>
+      <c r="M31" s="47" t="n"/>
+      <c r="N31" s="47" t="n"/>
+      <c r="O31" s="47" t="n"/>
+      <c r="P31" s="47" t="n"/>
+      <c r="Q31" s="47" t="n"/>
+      <c r="R31" s="47" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"新規,対応中,商談中,見積提出,契約済,請求済,入金済,見送り"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"資料請求,見学会予約,無料相談,AIチャット"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="44" t="inlineStr">
+        <is>
+          <t>工務店名</t>
+        </is>
+      </c>
+      <c r="C1" s="44" t="inlineStr">
+        <is>
+          <t>フリープラン開始日</t>
+        </is>
+      </c>
+      <c r="D1" s="44" t="inlineStr">
+        <is>
+          <t>3ヶ月経過日</t>
+        </is>
+      </c>
+      <c r="E1" s="44" t="inlineStr">
+        <is>
+          <t>月間PV</t>
+        </is>
+      </c>
+      <c r="F1" s="44" t="inlineStr">
+        <is>
+          <t>累計リード件数</t>
+        </is>
+      </c>
+      <c r="G1" s="44" t="inlineStr">
+        <is>
+          <t>有料化提案日</t>
+        </is>
+      </c>
+      <c r="H1" s="44" t="inlineStr">
+        <is>
+          <t>提案プラン</t>
+        </is>
+      </c>
+      <c r="I1" s="44" t="inlineStr">
+        <is>
+          <t>工務店回答</t>
+        </is>
+      </c>
+      <c r="J1" s="44" t="inlineStr">
+        <is>
+          <t>有料開始日</t>
+        </is>
+      </c>
+      <c r="K1" s="44" t="inlineStr">
+        <is>
+          <t>月額</t>
+        </is>
+      </c>
+      <c r="L1" s="44" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="M1" s="44" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="N1" s="44" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="49">
+        <f>IF(C2="","",C2+90)</f>
+        <v/>
+      </c>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="45" t="n"/>
+      <c r="K2" s="45" t="n"/>
+      <c r="L2" s="45" t="n"/>
+      <c r="M2" s="45" t="n"/>
+      <c r="N2" s="45" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="47" t="n"/>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="50">
+        <f>IF(C3="","",C3+90)</f>
+        <v/>
+      </c>
+      <c r="E3" s="47" t="n"/>
+      <c r="F3" s="47" t="n"/>
+      <c r="G3" s="47" t="n"/>
+      <c r="H3" s="47" t="n"/>
+      <c r="I3" s="47" t="n"/>
+      <c r="J3" s="47" t="n"/>
+      <c r="K3" s="47" t="n"/>
+      <c r="L3" s="47" t="n"/>
+      <c r="M3" s="47" t="n"/>
+      <c r="N3" s="47" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="49">
+        <f>IF(C4="","",C4+90)</f>
+        <v/>
+      </c>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="45" t="n"/>
+      <c r="L4" s="45" t="n"/>
+      <c r="M4" s="45" t="n"/>
+      <c r="N4" s="45" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="50">
+        <f>IF(C5="","",C5+90)</f>
+        <v/>
+      </c>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="47" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="49">
+        <f>IF(C6="","",C6+90)</f>
+        <v/>
+      </c>
+      <c r="E6" s="45" t="n"/>
+      <c r="F6" s="45" t="n"/>
+      <c r="G6" s="45" t="n"/>
+      <c r="H6" s="45" t="n"/>
+      <c r="I6" s="45" t="n"/>
+      <c r="J6" s="45" t="n"/>
+      <c r="K6" s="45" t="n"/>
+      <c r="L6" s="45" t="n"/>
+      <c r="M6" s="45" t="n"/>
+      <c r="N6" s="45" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="47" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="50">
+        <f>IF(C7="","",C7+90)</f>
+        <v/>
+      </c>
+      <c r="E7" s="47" t="n"/>
+      <c r="F7" s="47" t="n"/>
+      <c r="G7" s="47" t="n"/>
+      <c r="H7" s="47" t="n"/>
+      <c r="I7" s="47" t="n"/>
+      <c r="J7" s="47" t="n"/>
+      <c r="K7" s="47" t="n"/>
+      <c r="L7" s="47" t="n"/>
+      <c r="M7" s="47" t="n"/>
+      <c r="N7" s="47" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="49">
+        <f>IF(C8="","",C8+90)</f>
+        <v/>
+      </c>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="45" t="n"/>
+      <c r="G8" s="45" t="n"/>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="45" t="n"/>
+      <c r="J8" s="45" t="n"/>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="n"/>
+      <c r="M8" s="45" t="n"/>
+      <c r="N8" s="45" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="47" t="n"/>
+      <c r="C9" s="47" t="n"/>
+      <c r="D9" s="50">
+        <f>IF(C9="","",C9+90)</f>
+        <v/>
+      </c>
+      <c r="E9" s="47" t="n"/>
+      <c r="F9" s="47" t="n"/>
+      <c r="G9" s="47" t="n"/>
+      <c r="H9" s="47" t="n"/>
+      <c r="I9" s="47" t="n"/>
+      <c r="J9" s="47" t="n"/>
+      <c r="K9" s="47" t="n"/>
+      <c r="L9" s="47" t="n"/>
+      <c r="M9" s="47" t="n"/>
+      <c r="N9" s="47" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="49">
+        <f>IF(C10="","",C10+90)</f>
+        <v/>
+      </c>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="45" t="n"/>
+      <c r="H10" s="45" t="n"/>
+      <c r="I10" s="45" t="n"/>
+      <c r="J10" s="45" t="n"/>
+      <c r="K10" s="45" t="n"/>
+      <c r="L10" s="45" t="n"/>
+      <c r="M10" s="45" t="n"/>
+      <c r="N10" s="45" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="47" t="n"/>
+      <c r="C11" s="47" t="n"/>
+      <c r="D11" s="50">
+        <f>IF(C11="","",C11+90)</f>
+        <v/>
+      </c>
+      <c r="E11" s="47" t="n"/>
+      <c r="F11" s="47" t="n"/>
+      <c r="G11" s="47" t="n"/>
+      <c r="H11" s="47" t="n"/>
+      <c r="I11" s="47" t="n"/>
+      <c r="J11" s="47" t="n"/>
+      <c r="K11" s="47" t="n"/>
+      <c r="L11" s="47" t="n"/>
+      <c r="M11" s="47" t="n"/>
+      <c r="N11" s="47" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="49">
+        <f>IF(C12="","",C12+90)</f>
+        <v/>
+      </c>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="45" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="45" t="n"/>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="45" t="n"/>
+      <c r="M12" s="45" t="n"/>
+      <c r="N12" s="45" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="47" t="n"/>
+      <c r="D13" s="50">
+        <f>IF(C13="","",C13+90)</f>
+        <v/>
+      </c>
+      <c r="E13" s="47" t="n"/>
+      <c r="F13" s="47" t="n"/>
+      <c r="G13" s="47" t="n"/>
+      <c r="H13" s="47" t="n"/>
+      <c r="I13" s="47" t="n"/>
+      <c r="J13" s="47" t="n"/>
+      <c r="K13" s="47" t="n"/>
+      <c r="L13" s="47" t="n"/>
+      <c r="M13" s="47" t="n"/>
+      <c r="N13" s="47" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="45" t="n"/>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="49">
+        <f>IF(C14="","",C14+90)</f>
+        <v/>
+      </c>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="45" t="n"/>
+      <c r="G14" s="45" t="n"/>
+      <c r="H14" s="45" t="n"/>
+      <c r="I14" s="45" t="n"/>
+      <c r="J14" s="45" t="n"/>
+      <c r="K14" s="45" t="n"/>
+      <c r="L14" s="45" t="n"/>
+      <c r="M14" s="45" t="n"/>
+      <c r="N14" s="45" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="47" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="50">
+        <f>IF(C15="","",C15+90)</f>
+        <v/>
+      </c>
+      <c r="E15" s="47" t="n"/>
+      <c r="F15" s="47" t="n"/>
+      <c r="G15" s="47" t="n"/>
+      <c r="H15" s="47" t="n"/>
+      <c r="I15" s="47" t="n"/>
+      <c r="J15" s="47" t="n"/>
+      <c r="K15" s="47" t="n"/>
+      <c r="L15" s="47" t="n"/>
+      <c r="M15" s="47" t="n"/>
+      <c r="N15" s="47" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="49">
+        <f>IF(C16="","",C16+90)</f>
+        <v/>
+      </c>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="45" t="n"/>
+      <c r="G16" s="45" t="n"/>
+      <c r="H16" s="45" t="n"/>
+      <c r="I16" s="45" t="n"/>
+      <c r="J16" s="45" t="n"/>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="45" t="n"/>
+      <c r="M16" s="45" t="n"/>
+      <c r="N16" s="45" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="47" t="n"/>
+      <c r="C17" s="47" t="n"/>
+      <c r="D17" s="50">
+        <f>IF(C17="","",C17+90)</f>
+        <v/>
+      </c>
+      <c r="E17" s="47" t="n"/>
+      <c r="F17" s="47" t="n"/>
+      <c r="G17" s="47" t="n"/>
+      <c r="H17" s="47" t="n"/>
+      <c r="I17" s="47" t="n"/>
+      <c r="J17" s="47" t="n"/>
+      <c r="K17" s="47" t="n"/>
+      <c r="L17" s="47" t="n"/>
+      <c r="M17" s="47" t="n"/>
+      <c r="N17" s="47" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="49">
+        <f>IF(C18="","",C18+90)</f>
+        <v/>
+      </c>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+      <c r="H18" s="45" t="n"/>
+      <c r="I18" s="45" t="n"/>
+      <c r="J18" s="45" t="n"/>
+      <c r="K18" s="45" t="n"/>
+      <c r="L18" s="45" t="n"/>
+      <c r="M18" s="45" t="n"/>
+      <c r="N18" s="45" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="50">
+        <f>IF(C19="","",C19+90)</f>
+        <v/>
+      </c>
+      <c r="E19" s="47" t="n"/>
+      <c r="F19" s="47" t="n"/>
+      <c r="G19" s="47" t="n"/>
+      <c r="H19" s="47" t="n"/>
+      <c r="I19" s="47" t="n"/>
+      <c r="J19" s="47" t="n"/>
+      <c r="K19" s="47" t="n"/>
+      <c r="L19" s="47" t="n"/>
+      <c r="M19" s="47" t="n"/>
+      <c r="N19" s="47" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="45" t="n"/>
+      <c r="C20" s="45" t="n"/>
+      <c r="D20" s="49">
+        <f>IF(C20="","",C20+90)</f>
+        <v/>
+      </c>
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="45" t="n"/>
+      <c r="G20" s="45" t="n"/>
+      <c r="H20" s="45" t="n"/>
+      <c r="I20" s="45" t="n"/>
+      <c r="J20" s="45" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="45" t="n"/>
+      <c r="N20" s="45" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="50">
+        <f>IF(C21="","",C21+90)</f>
+        <v/>
+      </c>
+      <c r="E21" s="47" t="n"/>
+      <c r="F21" s="47" t="n"/>
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
+      <c r="I21" s="47" t="n"/>
+      <c r="J21" s="47" t="n"/>
+      <c r="K21" s="47" t="n"/>
+      <c r="L21" s="47" t="n"/>
+      <c r="M21" s="47" t="n"/>
+      <c r="N21" s="47" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="49">
+        <f>IF(C22="","",C22+90)</f>
+        <v/>
+      </c>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="45" t="n"/>
+      <c r="G22" s="45" t="n"/>
+      <c r="H22" s="45" t="n"/>
+      <c r="I22" s="45" t="n"/>
+      <c r="J22" s="45" t="n"/>
+      <c r="K22" s="45" t="n"/>
+      <c r="L22" s="45" t="n"/>
+      <c r="M22" s="45" t="n"/>
+      <c r="N22" s="45" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="47" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="50">
+        <f>IF(C23="","",C23+90)</f>
+        <v/>
+      </c>
+      <c r="E23" s="47" t="n"/>
+      <c r="F23" s="47" t="n"/>
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
+      <c r="I23" s="47" t="n"/>
+      <c r="J23" s="47" t="n"/>
+      <c r="K23" s="47" t="n"/>
+      <c r="L23" s="47" t="n"/>
+      <c r="M23" s="47" t="n"/>
+      <c r="N23" s="47" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="45" t="n"/>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="49">
+        <f>IF(C24="","",C24+90)</f>
+        <v/>
+      </c>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="45" t="n"/>
+      <c r="G24" s="45" t="n"/>
+      <c r="H24" s="45" t="n"/>
+      <c r="I24" s="45" t="n"/>
+      <c r="J24" s="45" t="n"/>
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+      <c r="N24" s="45" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="47" t="n"/>
+      <c r="C25" s="47" t="n"/>
+      <c r="D25" s="50">
+        <f>IF(C25="","",C25+90)</f>
+        <v/>
+      </c>
+      <c r="E25" s="47" t="n"/>
+      <c r="F25" s="47" t="n"/>
+      <c r="G25" s="47" t="n"/>
+      <c r="H25" s="47" t="n"/>
+      <c r="I25" s="47" t="n"/>
+      <c r="J25" s="47" t="n"/>
+      <c r="K25" s="47" t="n"/>
+      <c r="L25" s="47" t="n"/>
+      <c r="M25" s="47" t="n"/>
+      <c r="N25" s="47" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="45" t="n"/>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="49">
+        <f>IF(C26="","",C26+90)</f>
+        <v/>
+      </c>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="45" t="n"/>
+      <c r="G26" s="45" t="n"/>
+      <c r="H26" s="45" t="n"/>
+      <c r="I26" s="45" t="n"/>
+      <c r="J26" s="45" t="n"/>
+      <c r="K26" s="45" t="n"/>
+      <c r="L26" s="45" t="n"/>
+      <c r="M26" s="45" t="n"/>
+      <c r="N26" s="45" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="47" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="50">
+        <f>IF(C27="","",C27+90)</f>
+        <v/>
+      </c>
+      <c r="E27" s="47" t="n"/>
+      <c r="F27" s="47" t="n"/>
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="47" t="n"/>
+      <c r="I27" s="47" t="n"/>
+      <c r="J27" s="47" t="n"/>
+      <c r="K27" s="47" t="n"/>
+      <c r="L27" s="47" t="n"/>
+      <c r="M27" s="47" t="n"/>
+      <c r="N27" s="47" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="45" t="n"/>
+      <c r="C28" s="45" t="n"/>
+      <c r="D28" s="49">
+        <f>IF(C28="","",C28+90)</f>
+        <v/>
+      </c>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="45" t="n"/>
+      <c r="G28" s="45" t="n"/>
+      <c r="H28" s="45" t="n"/>
+      <c r="I28" s="45" t="n"/>
+      <c r="J28" s="45" t="n"/>
+      <c r="K28" s="45" t="n"/>
+      <c r="L28" s="45" t="n"/>
+      <c r="M28" s="45" t="n"/>
+      <c r="N28" s="45" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="47" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="47" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="50">
+        <f>IF(C29="","",C29+90)</f>
+        <v/>
+      </c>
+      <c r="E29" s="47" t="n"/>
+      <c r="F29" s="47" t="n"/>
+      <c r="G29" s="47" t="n"/>
+      <c r="H29" s="47" t="n"/>
+      <c r="I29" s="47" t="n"/>
+      <c r="J29" s="47" t="n"/>
+      <c r="K29" s="47" t="n"/>
+      <c r="L29" s="47" t="n"/>
+      <c r="M29" s="47" t="n"/>
+      <c r="N29" s="47" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="45" t="n"/>
+      <c r="D30" s="49">
+        <f>IF(C30="","",C30+90)</f>
+        <v/>
+      </c>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="45" t="n"/>
+      <c r="H30" s="45" t="n"/>
+      <c r="I30" s="45" t="n"/>
+      <c r="J30" s="45" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="45" t="n"/>
+      <c r="N30" s="45" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="47" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="47" t="n"/>
+      <c r="C31" s="47" t="n"/>
+      <c r="D31" s="50">
+        <f>IF(C31="","",C31+90)</f>
+        <v/>
+      </c>
+      <c r="E31" s="47" t="n"/>
+      <c r="F31" s="47" t="n"/>
+      <c r="G31" s="47" t="n"/>
+      <c r="H31" s="47" t="n"/>
+      <c r="I31" s="47" t="n"/>
+      <c r="J31" s="47" t="n"/>
+      <c r="K31" s="47" t="n"/>
+      <c r="L31" s="47" t="n"/>
+      <c r="M31" s="47" t="n"/>
+      <c r="N31" s="47" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"成果報酬,掲載ベーシック,掲載プロ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"フリープラン中,提案準備中,提案済,検討中,契約済,見送り,解約"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/04_営業ツール/管理シート/営業管理（テレアポ・戦略・料金）.xlsx
+++ b/docs/04_営業ツール/管理シート/営業管理（テレアポ・戦略・料金）.xlsx
@@ -263,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -376,6 +376,9 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6764,7 +6767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6789,6 +6792,12 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6900,6 +6909,36 @@
       <c r="V1" s="14" t="inlineStr">
         <is>
           <t>メモ</t>
+        </is>
+      </c>
+      <c r="W1" s="51" t="inlineStr">
+        <is>
+          <t>有料化提案日</t>
+        </is>
+      </c>
+      <c r="X1" s="51" t="inlineStr">
+        <is>
+          <t>提案プラン</t>
+        </is>
+      </c>
+      <c r="Y1" s="51" t="inlineStr">
+        <is>
+          <t>工務店回答</t>
+        </is>
+      </c>
+      <c r="Z1" s="51" t="inlineStr">
+        <is>
+          <t>有料開始日</t>
+        </is>
+      </c>
+      <c r="AA1" s="51" t="inlineStr">
+        <is>
+          <t>月額</t>
+        </is>
+      </c>
+      <c r="AB1" s="51" t="inlineStr">
+        <is>
+          <t>有料化ステータス</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12452,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:V101"/>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation sqref="T2 T3 T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 T52 T53 T54 T55 T56 T57 T58 T59 T60 T61 T62 T63 T64 T65 T66 T67 T68 T69 T70 T71 T72 T73 T74 T75 T76 T77 T78 T79 T80 T81 T82 T83 T84 T85 T86 T87 T88 T89 T90 T91 T92 T93 T94 T95 T96 T97 T98 T99 T100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="無効な値" error="選択肢から選んでください" type="list">
       <formula1>"未コール,コール済み,資料送付済み,商談調整中,商談済み,申込済み,見送り"</formula1>
     </dataValidation>
@@ -12422,6 +12461,12 @@
     </dataValidation>
     <dataValidation sqref="S2 S3 S4 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 S38 S39 S40 S41 S42 S43 S44 S45 S46 S47 S48 S49 S50 S51 S52 S53 S54 S55 S56 S57 S58 S59 S60 S61 S62 S63 S64 S65 S66 S67 S68 S69 S70 S71 S72 S73 S74 S75 S76 S77 S78 S79 S80 S81 S82 S83 S84 S85 S86 S87 S88 S89 S90 S91 S92 S93 S94 S95 S96 S97 S98 S99 S100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="無効な値" error="選択肢から選んでください" type="list">
       <formula1>"フリープラン,成果報酬,掲載ベーシック,掲載プロ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="X2 X3 X4 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X35 X36 X37 X38 X39 X40 X41 X42 X43 X44 X45 X46 X47 X48 X49 X50 X51 X52 X53 X54 X55 X56 X57 X58 X59 X60 X61 X62 X63 X64 X65 X66 X67 X68 X69 X70 X71 X72 X73 X74 X75 X76 X77 X78 X79 X80 X81 X82 X83 X84 X85 X86 X87 X88 X89 X90 X91 X92 X93 X94 X95 X96 X97 X98 X99 X100 X101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"成果報酬,掲載ベーシック,掲載プロ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB2 AB3 AB4 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30 AB31 AB32 AB33 AB34 AB35 AB36 AB37 AB38 AB39 AB40 AB41 AB42 AB43 AB44 AB45 AB46 AB47 AB48 AB49 AB50 AB51 AB52 AB53 AB54 AB55 AB56 AB57 AB58 AB59 AB60 AB61 AB62 AB63 AB64 AB65 AB66 AB67 AB68 AB69 AB70 AB71 AB72 AB73 AB74 AB75 AB76 AB77 AB78 AB79 AB80 AB81 AB82 AB83 AB84 AB85 AB86 AB87 AB88 AB89 AB90 AB91 AB92 AB93 AB94 AB95 AB96 AB97 AB98 AB99 AB100 AB101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"フリープラン中,提案準備中,提案済,検討中,契約済,見送り"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/04_営業ツール/管理シート/営業管理（テレアポ・戦略・料金）.xlsx
+++ b/docs/04_営業ツール/管理シート/営業管理（テレアポ・戦略・料金）.xlsx
@@ -1550,7 +1550,7 @@
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>資料請求</t>
+          <t>AI診断完了</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>資料請求or見学会予約1件以上 or 月間閲覧100回以上</t>
+          <t>会員登録or見学会予約1件以上 or 月間閲覧100回以上</t>
         </is>
       </c>
       <c r="C10" s="40" t="n"/>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>資料請求</t>
+          <t>AI家づくり診断</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
